--- a/重点商品CA別進捗_2026年7月.xlsx
+++ b/重点商品CA別進捗_2026年7月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +213,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -239,34 +239,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -292,28 +271,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -377,6 +335,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -427,7 +393,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -453,34 +419,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -506,28 +451,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -591,6 +515,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -641,7 +573,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -661,19 +593,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -694,12 +620,6 @@
               </pt>
               <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -763,6 +683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -813,7 +741,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -833,19 +761,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -865,12 +787,6 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -935,6 +851,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -985,7 +909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1005,19 +929,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1037,13 +955,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1107,6 +1019,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1157,7 +1077,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1177,19 +1097,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1210,12 +1124,6 @@
               </pt>
               <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1279,6 +1187,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1329,7 +1245,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1349,19 +1265,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1381,13 +1291,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1451,6 +1355,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1501,7 +1413,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1521,19 +1433,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1553,13 +1459,7 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1605,7 +1505,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1623,6 +1523,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1673,7 +1581,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1693,19 +1601,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1725,12 +1627,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1795,6 +1691,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1845,7 +1749,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1865,19 +1769,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -1897,13 +1795,7 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -1967,6 +1859,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2017,7 +1917,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2037,19 +1937,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2070,12 +1964,6 @@
               </pt>
               <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2139,6 +2027,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2189,7 +2085,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -2215,34 +2111,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>5</v>
               </pt>
@@ -2268,28 +2143,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>2</v>
-              </pt>
-              <pt idx="12">
-                <v>3</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -2335,7 +2189,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2353,6 +2207,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2403,7 +2265,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2423,19 +2285,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2455,12 +2311,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2525,6 +2375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2575,7 +2433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2592,22 +2450,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -2625,15 +2474,6 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2697,6 +2537,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2747,7 +2595,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2764,22 +2612,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
@@ -2796,16 +2635,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>4</v>
               </pt>
             </numLit>
           </val>
@@ -2869,6 +2699,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2919,7 +2757,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2936,22 +2774,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2968,15 +2797,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3041,6 +2861,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3091,7 +2919,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3108,22 +2936,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>6</v>
               </pt>
@@ -3140,16 +2959,7 @@
                 <v>3</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3213,6 +3023,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3263,7 +3081,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3280,22 +3098,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -3312,16 +3121,7 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -3385,6 +3185,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3435,7 +3243,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3452,22 +3260,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>6</v>
               </pt>
@@ -3484,16 +3283,7 @@
                 <v>2</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3557,6 +3347,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3607,7 +3405,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3624,22 +3422,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -3656,15 +3445,6 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3729,6 +3509,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3779,7 +3567,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3796,22 +3584,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -3828,16 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3901,6 +3671,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3951,7 +3729,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3968,22 +3746,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4000,16 +3769,7 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>1</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -4073,6 +3833,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4123,7 +3891,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -4149,34 +3917,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4202,28 +3949,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -4269,7 +3995,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -4287,6 +4013,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4337,7 +4071,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4354,22 +4088,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>阿部　隆二</v>
-              </pt>
-              <pt idx="7">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="8">
-                <v>秋山　泰賢</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -4386,15 +4111,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>1</v>
               </pt>
             </numLit>
@@ -4459,6 +4175,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4509,7 +4233,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4520,16 +4244,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -4540,9 +4261,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4607,6 +4325,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4657,7 +4383,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4668,16 +4394,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -4689,9 +4412,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -4755,6 +4475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4805,7 +4533,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4816,16 +4544,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -4836,9 +4561,6 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4903,6 +4625,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4953,7 +4683,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -4964,16 +4694,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>7</v>
               </pt>
@@ -4984,9 +4711,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -5051,6 +4775,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5101,7 +4833,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5112,16 +4844,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -5133,9 +4862,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5199,6 +4925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5249,7 +4983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5260,16 +4994,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>9</v>
               </pt>
@@ -5280,9 +5011,6 @@
                 <v>1</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -5347,6 +5075,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5397,7 +5133,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5408,16 +5144,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -5429,9 +5162,6 @@
               </pt>
               <pt idx="3">
                 <v>1</v>
-              </pt>
-              <pt idx="4">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5495,6 +5225,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5545,7 +5283,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5556,16 +5294,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>9</v>
               </pt>
@@ -5576,10 +5311,7 @@
                 <v>8</v>
               </pt>
               <pt idx="3">
-                <v>2</v>
-              </pt>
-              <pt idx="4">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -5643,6 +5375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5693,7 +5433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -5704,16 +5444,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -5724,9 +5461,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -5791,6 +5525,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5841,7 +5583,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -5867,34 +5609,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -5920,28 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>1</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -6005,6 +5705,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6055,7 +5763,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>山本　雅巳</v>
               </pt>
@@ -6066,16 +5774,13 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="4">
-                <v>竹内　杏</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="5"/>
+              <ptCount val="4"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -6086,9 +5791,6 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
-              </pt>
-              <pt idx="4">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6153,6 +5855,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6203,22 +5913,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6283,6 +5999,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6333,22 +6057,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6413,6 +6143,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6463,23 +6201,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6525,7 +6269,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6543,6 +6287,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6593,23 +6345,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>12</v>
               </pt>
               <pt idx="1">
                 <v>6</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6673,6 +6431,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6723,23 +6489,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>5</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6803,6 +6575,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6853,23 +6633,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>8</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6933,6 +6719,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6983,23 +6777,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>8</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -7063,6 +6863,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7113,23 +6921,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>14</v>
               </pt>
               <pt idx="1">
                 <v>6</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -7193,6 +7007,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7243,22 +7065,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7305,7 +7133,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7323,6 +7151,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7373,7 +7209,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -7399,34 +7235,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -7452,28 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>4</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>2</v>
-              </pt>
-              <pt idx="13">
-                <v>1</v>
-              </pt>
-              <pt idx="14">
-                <v>1</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -7519,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="9"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7537,6 +7331,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7587,23 +7389,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -7667,6 +7475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7725,7 +7541,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7803,6 +7619,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7861,7 +7685,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7921,7 +7745,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7939,6 +7763,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7997,7 +7829,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8057,7 +7889,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8075,6 +7907,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8133,7 +7973,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8211,6 +8051,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8269,7 +8117,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8347,6 +8195,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8405,7 +8261,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8465,7 +8321,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8483,6 +8339,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8541,7 +8405,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8619,6 +8483,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8677,7 +8549,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8755,6 +8627,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8813,7 +8693,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8891,6 +8771,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8941,7 +8829,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -8967,34 +8855,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -9020,28 +8887,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>3</v>
-              </pt>
-              <pt idx="13">
-                <v>1</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
+                <v>7</v>
               </pt>
             </numLit>
           </val>
@@ -9087,7 +8933,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9105,6 +8951,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9163,7 +9017,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -9223,7 +9077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9241,6 +9095,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9380,6 +9242,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9519,6 +9389,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9658,6 +9536,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9797,6 +9683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9936,6 +9830,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10075,6 +9977,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10214,6 +10124,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10353,6 +10271,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10492,6 +10418,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10542,7 +10476,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10568,34 +10502,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -10621,27 +10534,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10706,6 +10598,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10845,6 +10745,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10895,7 +10803,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10921,34 +10829,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -10974,28 +10861,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>7</v>
-              </pt>
-              <pt idx="12">
-                <v>1</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>1</v>
+                <v>9</v>
               </pt>
             </numLit>
           </val>
@@ -11059,6 +10925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11109,7 +10983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -11135,34 +11009,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="9">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="10">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="11">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="12">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="13">
-                <v>中原　義美</v>
-              </pt>
-              <pt idx="14">
-                <v>杉澤　修平</v>
-              </pt>
-              <pt idx="15">
-                <v>落合　典彦</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="16"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -11188,28 +11041,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
                 <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
-              </pt>
-              <pt idx="14">
-                <v>0</v>
-              </pt>
-              <pt idx="15">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -11273,6 +11105,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11285,7 +11125,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11307,7 +11147,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11329,7 +11169,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11351,7 +11191,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11373,7 +11213,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11395,7 +11235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11417,7 +11257,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11439,7 +11279,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11461,7 +11301,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11483,7 +11323,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11510,7 +11350,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11532,7 +11372,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11554,7 +11394,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11576,7 +11416,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11598,7 +11438,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11620,7 +11460,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11642,7 +11482,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11664,7 +11504,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11686,7 +11526,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11708,7 +11548,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11735,7 +11575,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11757,7 +11597,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11779,7 +11619,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11801,7 +11641,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11823,7 +11663,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11845,7 +11685,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11867,7 +11707,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11889,7 +11729,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11911,7 +11751,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11933,7 +11773,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11960,7 +11800,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11982,7 +11822,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12004,7 +11844,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12026,7 +11866,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12048,7 +11888,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12070,7 +11910,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12092,7 +11932,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12114,7 +11954,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12136,7 +11976,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12158,7 +11998,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12185,7 +12025,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12207,7 +12047,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12229,7 +12069,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12251,7 +12091,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12273,7 +12113,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12295,7 +12135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12317,7 +12157,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12339,7 +12179,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12361,7 +12201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12383,7 +12223,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12410,7 +12250,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12432,7 +12272,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12454,7 +12294,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12476,7 +12316,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12498,7 +12338,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12520,7 +12360,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12542,7 +12382,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12564,7 +12404,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12586,7 +12426,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12608,7 +12448,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12635,7 +12475,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12657,7 +12497,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12679,7 +12519,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12701,7 +12541,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12723,7 +12563,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12745,7 +12585,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12767,7 +12607,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12789,7 +12629,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12811,7 +12651,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12833,7 +12673,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -13140,741 +12980,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42.48" customWidth="1" min="1" max="1"/>
-    <col width="42.48" customWidth="1" min="2" max="2"/>
-    <col width="42.48" customWidth="1" min="3" max="3"/>
-    <col width="42.48" customWidth="1" min="4" max="4"/>
-    <col width="42.48" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>加
-藤
-英
-基</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>川
-村
-正
-敏</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>村
-上
-英
-俊</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>野
-呂
-藍
-亮</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>小
-野
-翼</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>橋
-本
-隆
-志</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>岩
-坪
-公
-夫</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>中
-原
-義
-美</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>杉
-澤
-修
-平</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>落
-合
-典
-彦</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>エンジンリフレッシュ</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>エアコン潤滑剤 NC200マキシクール</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ウィンドウ撥水12カ月</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>エアコン/ヒーター洗浄12カ月</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>メタルトリートメント MT-10</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>クーラントエナジー</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>抗菌・抗ウィルスコート</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>ボディーコート3カ月</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>NISMOオイル / Mobil1オイル （台数）</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>ギヤボックス添加剤　SuperADD1201</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13898,12 +13003,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
+          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13911,80 +13016,76 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>大
-島
-貞
-男</t>
+          <t>加
+藤
+英
+基</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>杉
-澤
-修
-平</t>
+          <t>川
+村
+正
+敏</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>平
-館
-健</t>
+          <t>村
+上
+英
+俊</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>平
-賀
-崇</t>
+          <t>阿
+部
+隆
+二</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>安
-部
-雅
-史</t>
+          <t>野
+呂
+藍
+亮</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>田
-中
-智
-久</t>
+          <t>小
+野
+翼</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>橋
+本
+隆
+志</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>前
-野
-正
-樹</t>
+          <t>岩
+坪
+公
+夫</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>秋
-山
-泰
-賢</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -13997,50 +13098,50 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>0</v>
@@ -14049,10 +13150,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14065,35 +13166,35 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -14102,25 +13203,25 @@
         <v>3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14130,28 +13231,28 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -14161,16 +13262,16 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>1</v>
@@ -14179,13 +13280,13 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -14195,10 +13296,10 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>3</v>
@@ -14229,31 +13330,31 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -14263,31 +13364,31 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14303,10 +13404,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
@@ -14321,23 +13422,24 @@
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14353,19 +13455,17 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">神山店 CA別進捗(重点10商品) </t>
+          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14373,149 +13473,115 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>水
-嶋
-規
-雄</t>
+          <t>大
+島
+貞
+男</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>竹
-村
-優
-希</t>
+          <t>杉
+澤
+修
+平</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>竹
-内
-杏</t>
+          <t>平
+館
+健</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>芳
+          <t>平
 賀
-芳
-勝</t>
+崇</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>中
-原
-義
-美</t>
+          <t>安
+部
+雅
+史</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>落
-合
-典
-彦</t>
+          <t>田
+中
+智
+久</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>阿
-部
-隆
-二</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14528,93 +13594,75 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14624,31 +13672,25 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -14658,30 +13700,24 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14695,28 +13731,22 @@
         <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -14729,28 +13759,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14760,13 +13784,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>0</v>
@@ -14779,28 +13803,23 @@
       </c>
       <c r="O13" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14814,6 +13833,347 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神山店 CA別進捗(重点10商品) </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="358.5826771653543" customHeight="1">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>水
+嶋
+規
+雄</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>竹
+村
+優
+希</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>竹
+内
+杏</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>芳
+賀
+芳
+勝</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>中
+原
+義
+美</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42.51968503937007" customHeight="1">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>エンジンリフレッシュ</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="358.5826771653543" customHeight="1">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>エアコン潤滑剤 NC200マキシクール</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ウィンドウ撥水12カ月</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>エアコン/ヒーター洗浄12カ月</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>メタルトリートメント MT-10</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>クーラントエナジー</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>抗菌・抗ウィルスコート</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>ボディーコート3カ月</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>NISMOオイル / Mobil1オイル （台数）</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>ギヤボックス添加剤　SuperADD1201</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.48" customWidth="1" min="1" max="1"/>
+    <col width="42.48" customWidth="1" min="2" max="2"/>
+    <col width="42.48" customWidth="1" min="3" max="3"/>
+    <col width="42.48" customWidth="1" min="4" max="4"/>
+    <col width="42.48" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14824,7 +14184,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14857,25 +14217,13 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>竹
-内
-杏</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14893,11 +14241,8 @@
       <c r="L4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14915,11 +14260,8 @@
       <c r="L5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14937,11 +14279,8 @@
       <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14959,11 +14298,8 @@
       <c r="L7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14980,9 +14316,6 @@
       </c>
       <c r="L8" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15003,9 +14336,6 @@
       <c r="L9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -15025,9 +14355,6 @@
       <c r="L10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15045,10 +14372,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -15069,9 +14393,6 @@
       <c r="L12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15091,11 +14412,9 @@
       <c r="L13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15108,7 +14427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -15119,6 +14438,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -15129,7 +14449,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15151,8 +14471,15 @@
 一</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15164,8 +14491,11 @@
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15177,8 +14507,11 @@
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15190,8 +14523,11 @@
       <c r="J6" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15203,8 +14539,11 @@
       <c r="J7" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -15215,6 +14554,9 @@
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15229,6 +14571,9 @@
       <c r="J9" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -15242,6 +14587,9 @@
       <c r="J10" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -15255,6 +14603,9 @@
       <c r="J11" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
@@ -15268,6 +14619,9 @@
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -15281,8 +14635,12 @@
       <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15317,7 +14675,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15341,18 +14699,13 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15368,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15384,7 +14737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15400,7 +14753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15416,7 +14769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -15513,6 +14866,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15549,7 +14903,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15595,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15617,7 +14971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15639,7 +14993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15661,7 +15015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15683,7 +15037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -15816,6 +15170,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
